--- a/artfynd/A 46874-2025 artfynd.xlsx
+++ b/artfynd/A 46874-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>112780508</v>
+        <v>128217217</v>
       </c>
       <c r="B2" t="n">
-        <v>89921</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5442</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -718,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>548132</v>
+        <v>548333</v>
       </c>
       <c r="R2" t="n">
-        <v>7074219</v>
+        <v>7074120</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -748,12 +743,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-10-17</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-10-17</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -781,15 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>112780499</v>
+        <v>112780508</v>
       </c>
       <c r="B3" t="n">
-        <v>77981</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -797,21 +787,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -824,10 +814,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>548063</v>
+        <v>548132</v>
       </c>
       <c r="R3" t="n">
-        <v>7074266</v>
+        <v>7074219</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -887,37 +877,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>112780497</v>
+        <v>112780499</v>
       </c>
       <c r="B4" t="n">
-        <v>74165</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -993,43 +978,37 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>112780487</v>
+        <v>112780497</v>
       </c>
       <c r="B5" t="n">
-        <v>97128</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1037,10 +1016,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>547938</v>
+        <v>548063</v>
       </c>
       <c r="R5" t="n">
-        <v>7074183</v>
+        <v>7074266</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1097,6 +1076,108 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>112780487</v>
+      </c>
+      <c r="B6" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Trångåsen, Ång</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>547938</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7074183</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Fjällsjö</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2023-10-17</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2023-10-17</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Maria Johansson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Maria Johansson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 46874-2025 artfynd.xlsx
+++ b/artfynd/A 46874-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128217217</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112780508</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112780499</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1076,6 +1096,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112780497</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1178,8 +1203,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112780487</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>